--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Légende" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UI_Textes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Textes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UI_Textes'!$A$1:$G$186</definedName>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G404"/>
+  <dimension ref="A1:G463"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14235,6 +14235,1894 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>accueil_bouton_creer_moadr</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Créer un MOADR</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Create a MOADR</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Een MOADR aanmaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>moadr_outil_titre</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>moadr_outil_sous_titre</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Mode Opératoire avec Analyse de Risque</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Method Statement with Risk Analysis</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Werkwijze met risicoanalyse</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>moadr_lie_chantier</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Lié au chantier</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Linked to site</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Gekoppeld aan de werf</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>moadr_lie_demande</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Répond à la demande MOADR de ce RePSS</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Answers the MOADR request from this RePSS</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Beantwoordt de MOADR-aanvraag van dit RePSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>moadr_s1_titre</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>1. Objet du Mode Opératoire</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>1. Purpose of the Method Statement</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>1. Doel van de werkwijze</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>moadr_projet</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>moadr_lieu</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Lieu de l'intervention</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Locatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>moadr_date_debut</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Date de début</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Startdatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>moadr_duree</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Durée</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Duur</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>moadr_responsable_operation</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Responsable de l'opération</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Person in charge</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Verantwoordelijke</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>moadr_s2_titre</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2. Description de l'Intervention</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>2. Description of the Work</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2. Beschrijving van de interventie</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>moadr_contexte</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Contexte</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>moadr_etapes_principales</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Étapes principales</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Main steps</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Belangrijkste stappen</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>moadr_s3_titre</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>3. Équipement et Matériel Utilisé</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>3. Equipment and Materials Used</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>3. Gebruikte uitrusting en materiaal</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>moadr_materiel</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Matériel (dimensions, type de matériau)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Materials (dimensions, type)</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Materiaal (afmetingen, type)</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>moadr_outils</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Outils</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Gereedschap</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>moadr_moyens_levage</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Moyens de levage</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Lifting equipment</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Hijsmiddelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>moadr_epi_utilises</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Équipements de protection individuelle (EPI)</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Personal protective equipment (PPE)</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Persoonlijke beschermingsmiddelen (PBM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>moadr_s4_titre</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>4. Ressources Humaines</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>4. Human Resources</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>4. Personeel</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>moadr_nombre_operateurs</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Nombre d'opérateurs impliqués</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Number of operators involved</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Aantal betrokken operatoren</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>moadr_qualification_operateurs</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Qualification des opérateurs</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Operators' qualification</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Kwalificatie van de operatoren</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>moadr_s5_titre</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>5. Analyse de Risque (Méthode Kinney)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>5. Risk Analysis (Kinney Method)</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>5. Risicoanalyse (Kinney-methode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>moadr_s5_1_titre</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>5.1 Introduction à la méthode Kinney</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>5.1 Introduction to the Kinney method</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>5.1 Inleiding tot de Kinney-methode</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>moadr_s5_1_texte</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>La méthode Kinney quantifie chaque risque à partir de trois facteurs : Probabilité, Exposition et Gravité. Le risque est calculé selon la formule R = Probabilité × Exposition × Gravité, sur la même échelle que le reste des documents RePSS (voir Annexe 1 — Légende Kinney).</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>The Kinney method quantifies each risk from three factors: Probability, Exposure and Severity. The risk is calculated using the formula R = Probability × Exposure × Severity, on the same scale as the rest of the RePSS documents (see Appendix 1 — Kinney Legend).</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>De Kinney-methode kwantificeert elk risico aan de hand van drie factoren: Waarschijnlijkheid, Blootstelling en Ernst. Het risico wordt berekend met de formule R = Waarschijnlijkheid × Blootstelling × Ernst, op dezelfde schaal als de rest van de RePSS-documenten (zie Bijlage 1 — Kinney-legende).</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>moadr_s5_2_titre</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>5.2 Tableau d'Analyse de Risques</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>5.2 Risk Analysis Table</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>5.2 Risicoanalysetabel</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>moadr_ligne_tache</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Tâche / étape</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Task / step</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Taak / stap</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>moadr_ligne_danger</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Danger</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Hazard</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Gevaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>moadr_ligne_situation</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Situation dangereuse</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Dangerous situation</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Gevaarlijke situatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>moadr_ligne_mesures_existantes</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Mesures existantes</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Existing measures</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Bestaande maatregelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>moadr_risque_initial</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Risque initial</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Initial risk</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Initieel risico</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>moadr_risque_residuel</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Risque résiduel</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Residual risk</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Restrisico</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>moadr_bouton_ajouter_ligne_risque</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Ajouter la ligne</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Add line</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Regel toevoegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>moadr_bouton_vider_tableau</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Vider le tableau</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Clear table</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Tabel leegmaken</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>moadr_confirmer_vider_tableau</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Vider tout le tableau d'analyse de risques ? Cette action est irréversible.</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Clear the entire risk analysis table? This action cannot be undone.</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>De volledige risicoanalysetabel leegmaken? Deze actie kan niet ongedaan worden gemaakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>moadr_aucune_ligne</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Aucune ligne d'analyse pour l'instant.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>No analysis line yet.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Nog geen analyseregel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>moadr_ref_ligne</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Réf.</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>moadr_action_necessaire</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Action nécessaire</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Action required</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Actie vereist</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>moadr_action_acceptable</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Aanvaardbaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>moadr_score_label</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Score R</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Score R</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Score R</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>moadr_s6_titre</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>6. Planification des Mesures de Prévention</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>6. Planning of Prevention Measures</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>6. Planning van preventiemaatregelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>moadr_epc</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>EPC (protections collectives)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Collective protection</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Collectieve bescherming</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>moadr_epi_mesures</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>PPE</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>PBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>moadr_zones_securite</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Zones de sécurité</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Safety zones</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Veiligheidszones</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>moadr_controle_echafaudages</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Contrôle des échafaudages</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Scaffolding control</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Controle van steigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>moadr_formations</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Formations</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Opleidingen</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>moadr_s7_titre</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>7. Procédure de Secours</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>7. Emergency Procedure</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>7. Noodprocedure</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>moadr_plan_secours</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Plan de secours interne</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Internal emergency plan</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Intern noodplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>moadr_point_assemblage</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Point d'assemblage en cas d'évacuation</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Assembly point in case of evacuation</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Verzamelpunt bij evacuatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>moadr_s8_titre</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>8. Suivi et Contrôles</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>8. Follow-up and Checks</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>8. Opvolging en controles</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>moadr_controle_quotidien</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Contrôle quotidien</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Daily check</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Dagelijkse controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>moadr_validation_installations</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Validation des installations</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Installation validation</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Validatie van de installaties</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>moadr_s9_titre</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>9. Signatures</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>9. Signatures</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>9. Handtekeningen</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>moadr_signature_responsable_operation</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Responsable de l'opération (PM)</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Person in charge (PM)</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Verantwoordelijke (PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>moadr_signature_sippt</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Responsable SIPPT</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>SIPPT Officer</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>IDPBW-verantwoordelijke</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>moadr_signature_operateurs</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Opérateurs</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Operators</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Operatoren</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>moadr_reference_attribuee</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Référence MOADR attribuée</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>MOADR reference assigned</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>MOADR-referentie toegekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>moadr_annexe_repss_mention</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Ce MOADR sera joint en annexe du RePSS lié.</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>This MOADR will be attached as an annex to the linked RePSS.</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Deze MOADR wordt als bijlage bij de gekoppelde RePSS gevoegd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>bouton_annuler</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Générique</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Annuler</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Annuleren</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G463"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16123,6 +16123,38 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>moadr_voir_tableau_page_suivante</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Voir le tableau détaillé, page suivante.</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>See the detailed table on the next page.</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Zie de gedetailleerde tabel op de volgende pagina.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G466"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15117,17 +15117,17 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Danger</t>
+          <t>Situation dangereuse (ex : travail point chaud)</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Hazard</t>
+          <t>Hazardous situation (e.g. hot work)</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Gevaar</t>
+          <t>Gevaarlijke situatie (bv. warm werk)</t>
         </is>
       </c>
     </row>
@@ -15149,17 +15149,17 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Situation dangereuse</t>
+          <t>Risque (ex : brûlure, incendie...)</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Dangerous situation</t>
+          <t>Risk (e.g. burn, fire...)</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Gevaarlijke situatie</t>
+          <t>Risico (bv. brandwonde, brand...)</t>
         </is>
       </c>
     </row>
@@ -15181,17 +15181,17 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Mesures existantes</t>
+          <t>Mesures à mettre en place</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Existing measures</t>
+          <t>Measures to implement</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Bestaande maatregelen</t>
+          <t>Te nemen maatregelen</t>
         </is>
       </c>
     </row>
@@ -16152,6 +16152,70 @@
       <c r="F464" t="inlineStr">
         <is>
           <t>Zie de gedetailleerde tabel op de volgende pagina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>moadr_ouvrir</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Ouvrir le MOADR</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Open the MOADR</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>MOADR openen</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>moadr_rouvrir</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Rouvrir le MOADR</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Reopen the MOADR</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>MOADR heropenen</t>
         </is>
       </c>
     </row>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G466"/>
+  <dimension ref="A1:G475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15021,17 +15021,17 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>La méthode Kinney quantifie chaque risque à partir de trois facteurs : Probabilité, Exposition et Gravité. Le risque est calculé selon la formule R = Probabilité × Exposition × Gravité, sur la même échelle que le reste des documents RePSS (voir Annexe 1 — Légende Kinney).</t>
+          <t>La méthode Kinney quantifie chaque risque à partir de trois facteurs : Probabilité, Exposition et Gravité. Le risque est calculé selon la formule R = Probabilité × Exposition × Gravité.</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>The Kinney method quantifies each risk from three factors: Probability, Exposure and Severity. The risk is calculated using the formula R = Probability × Exposure × Severity, on the same scale as the rest of the RePSS documents (see Appendix 1 — Kinney Legend).</t>
+          <t>The Kinney method quantifies each risk from three factors: Probability, Exposure and Severity. The risk is calculated using the formula R = Probability × Exposure × Severity.</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>De Kinney-methode kwantificeert elk risico aan de hand van drie factoren: Waarschijnlijkheid, Blootstelling en Ernst. Het risico wordt berekend met de formule R = Waarschijnlijkheid × Blootstelling × Ernst, op dezelfde schaal als de rest van de RePSS-documenten (zie Bijlage 1 — Kinney-legende).</t>
+          <t>De Kinney-methode kwantificeert elk risico aan de hand van drie factoren: Waarschijnlijkheid, Blootstelling en Ernst. Het risico wordt berekend met de formule R = Waarschijnlijkheid × Blootstelling × Ernst.</t>
         </is>
       </c>
     </row>
@@ -16216,6 +16216,294 @@
       <c r="F466" t="inlineStr">
         <is>
           <t>MOADR heropenen</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>moadr_kinney_p_titre</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Facteur de probabilité (P)</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Probability factor (P)</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Waarschijnlijkheidsfactor (P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>moadr_kinney_p_texte</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>La probabilité est le risque qu'un danger entraîne des dommages. Vous devez procéder à cette estimation sans tenir compte des mesures de prévention individuelles ou collectives.</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Probability is the risk that a hazard results in harm. This estimate must be made without taking individual or collective prevention measures into account.</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Waarschijnlijkheid is het risico dat een gevaar tot schade leidt. Deze inschatting moet gebeuren zonder rekening te houden met individuele of collectieve preventiemaatregelen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>moadr_kinney_e_titre</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Facteur d'exposition (E)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Exposure factor (E)</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Blootstellingsfactor (E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>moadr_kinney_e_texte</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Le facteur d'exposition tient compte de la durée et de la fréquence de l'exposition au danger.</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>The exposure factor takes into account the duration and frequency of exposure to the hazard.</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>De blootstellingsfactor houdt rekening met de duur en de frequentie van de blootstelling aan het gevaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>moadr_kinney_g_titre</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Degré de gravité (G)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Severity level (G)</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Ernstgraad (G)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>moadr_kinney_g_texte</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Pour estimer le degré de gravité, vous devez estimer les plus graves effets éventuels de l'exposition.</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>To estimate the severity level, you must estimate the most serious possible effects of the exposure.</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Om de ernstgraad in te schatten, moet u de ernstigste mogelijke gevolgen van de blootstelling inschatten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>moadr_importer_bouton</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Importer un fichier</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Import a file</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Een bestand importeren</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>moadr_importer_erreur</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Fichier invalide : ce n'est pas un MOADR (.json).</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Invalid file: this is not a MOADR (.json).</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Ongeldig bestand: dit is geen MOADR (.json).</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>moadr_importer_succes</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>MOADR importé.</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>MOADR imported.</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>MOADR geïmporteerd.</t>
         </is>
       </c>
     </row>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -8044,17 +8044,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Heures de chantier &lt; 1000</t>
+          <t>Heures de chantier &gt; 1000</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Site hours &lt; 1000</t>
+          <t>Site hours &gt; 1000</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Werfuren &lt; 1000</t>
+          <t>Werfuren &gt; 1000</t>
         </is>
       </c>
     </row>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_Textes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Légende" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UI_Textes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UI_Textes'!$A$1:$G$186</definedName>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G475"/>
+  <dimension ref="A1:G480"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16507,6 +16507,166 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>erreur_generation_pdf</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Générique</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Erreur lors de la génération du PDF. Réessaie, et si ça persiste, vérifie qu'aucun MOADR joint n'est corrompu.</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Error generating the PDF. Try again, and if it persists, check that no attached MOADR is corrupted.</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Fout bij het genereren van de PDF. Probeer opnieuw, en controleer bij aanhoudend probleem of geen gekoppelde MOADR beschadigd is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>moadr_statut_valide</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Validé — sera fusionné au PDF du RePSS</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Validated — will be merged into the RePSS PDF</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Gevalideerd — wordt samengevoegd met de RePSS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>moadr_bouton_valider</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Valider</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Validate</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Valideren</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>moadr_bouton_devalider</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Dévalider</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Unvalidate</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Validatie ongedaan maken</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>moadr_joint_en_annexe</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Joint en annexe de ce document (pages suivantes).</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Attached as an annex to this document (following pages).</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Als bijlage bij dit document gevoegd (volgende pagina's).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
